--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825263</v>
       </c>
       <c r="B2" t="n">
-        <v>96986</v>
+        <v>97154</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825263</v>
       </c>
       <c r="B2" t="n">
-        <v>97217</v>
+        <v>97219</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825263</v>
       </c>
       <c r="B2" t="n">
-        <v>97219</v>
+        <v>97223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825263</v>
       </c>
       <c r="B2" t="n">
-        <v>97223</v>
+        <v>97224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825263</v>
       </c>
       <c r="B2" t="n">
-        <v>97224</v>
+        <v>97226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825263</v>
       </c>
       <c r="B2" t="n">
-        <v>97226</v>
+        <v>97228</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825263</v>
       </c>
       <c r="B2" t="n">
-        <v>97228</v>
+        <v>97230</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825263</v>
       </c>
       <c r="B2" t="n">
-        <v>97230</v>
+        <v>97234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825263</v>
       </c>
       <c r="B2" t="n">
-        <v>97234</v>
+        <v>97237</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>124825263</v>
       </c>
       <c r="B2" t="n">
-        <v>97237</v>
+        <v>97246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124825263</v>
+        <v>67626357</v>
       </c>
       <c r="B2" t="n">
-        <v>97246</v>
+        <v>97461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -699,21 +699,17 @@
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Villingsberg, Nrk</t>
+          <t>Fräkenmossen, O om, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484534</v>
+        <v>484520</v>
       </c>
       <c r="R2" t="n">
-        <v>6574591</v>
+        <v>6574590</v>
       </c>
       <c r="S2" t="n">
         <v>75</v>
@@ -740,17 +736,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
+          <t>2002-01-01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>2002-12-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,15 +756,121 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Närkes Flora 2013</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124825263</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97246</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>224358</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig plattlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum subsp. complanatum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Villingsberg, Nrk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>484534</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6574591</v>
+      </c>
+      <c r="S3" t="n">
+        <v>75</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Karlskoga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Mimmi Persson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>67626357</v>
       </c>
       <c r="B2" t="n">
-        <v>97461</v>
+        <v>97467</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 20138-2025 artfynd.xlsx
+++ b/artfynd/A 20138-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>67626357</v>
       </c>
       <c r="B2" t="n">
-        <v>97467</v>
+        <v>97469</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
